--- a/result/train_info_resnet18_part_detrend_plr_stft_bin_win_fi.xlsx
+++ b/result/train_info_resnet18_part_detrend_plr_stft_bin_win_fi.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>train_loss</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>test_loss</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>test_acc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
@@ -480,28 +468,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5489462483203783</v>
+        <v>0.5308359296768239</v>
       </c>
       <c r="C2" t="n">
         <v>0.001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3831342618317294</v>
+        <v>0.4750552930422788</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8342623560014865</v>
+        <v>0.7857673727238944</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8046558704453441</v>
+        <v>0.8538708199725149</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8839881393624908</v>
+        <v>0.6908821349147517</v>
       </c>
       <c r="H2" t="n">
-        <v>0.842458495231367</v>
+        <v>0.7637779143618111</v>
       </c>
       <c r="I2" t="n">
-        <v>53.16005420684814</v>
+        <v>41.94536280632019</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +497,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3429931857987109</v>
+        <v>0.3469542290954498</v>
       </c>
       <c r="C3" t="n">
         <v>0.0009997532801828658</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2695774406900067</v>
+        <v>0.2434449368018723</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8861018208844296</v>
+        <v>0.9000371609067261</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9020439645198611</v>
+        <v>0.8930131004366813</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8669384729429207</v>
+        <v>0.9095626389918459</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8841428841428841</v>
+        <v>0.9012118986412045</v>
       </c>
       <c r="I3" t="n">
-        <v>54.05043005943298</v>
+        <v>42.00338530540466</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +526,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2608585480550777</v>
+        <v>0.2380288698576269</v>
       </c>
       <c r="C4" t="n">
         <v>0.0009990133642141358</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2051205180982161</v>
+        <v>0.1989960803611744</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9173169825343739</v>
+        <v>0.9149015235971758</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9062387306166606</v>
+        <v>0.9034582132564841</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9314306893995552</v>
+        <v>0.9295774647887324</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9186620361908243</v>
+        <v>0.9163317500913409</v>
       </c>
       <c r="I4" t="n">
-        <v>54.77010083198547</v>
+        <v>42.12934923171997</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +555,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1952949209805761</v>
+        <v>0.1715023693494377</v>
       </c>
       <c r="C5" t="n">
         <v>0.00099778098230154</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2005532703544261</v>
+        <v>0.2046756786817806</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9163879598662207</v>
+        <v>0.919732441471572</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9247921390778534</v>
+        <v>0.971297836938436</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9069681245366938</v>
+        <v>0.8654558932542624</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9157934131736527</v>
+        <v>0.915327322618581</v>
       </c>
       <c r="I5" t="n">
-        <v>55.78289675712585</v>
+        <v>42.16438174247742</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +584,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1667477669938845</v>
+        <v>0.1262357316089221</v>
       </c>
       <c r="C6" t="n">
         <v>0.000996057350657239</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1370040889906548</v>
+        <v>0.1523913508721974</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9464882943143813</v>
+        <v>0.9409141583054627</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9616858237547893</v>
+        <v>0.9103448275862069</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9303187546330616</v>
+        <v>0.9785025945144552</v>
       </c>
       <c r="H6" t="n">
-        <v>0.945742275810098</v>
+        <v>0.9431939978563773</v>
       </c>
       <c r="I6" t="n">
-        <v>56.28033447265625</v>
+        <v>42.04741740226746</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +613,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1264835669538684</v>
+        <v>0.1074206878750808</v>
       </c>
       <c r="C7" t="n">
         <v>0.0009938441702975688</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1211136433918624</v>
+        <v>0.1156362404209181</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9557785209959123</v>
+        <v>0.956893348197696</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9641509433962264</v>
+        <v>0.9363057324840764</v>
       </c>
       <c r="G7" t="n">
-        <v>0.946997776130467</v>
+        <v>0.9807264640474426</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9554973821989529</v>
+        <v>0.9580014482259233</v>
       </c>
       <c r="I7" t="n">
-        <v>57.182541847229</v>
+        <v>41.94177865982056</v>
       </c>
     </row>
     <row r="8">
@@ -654,28 +642,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1039564300682756</v>
+        <v>0.086748606768225</v>
       </c>
       <c r="C8" t="n">
         <v>0.0009911436253643444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1120311840101195</v>
+        <v>0.08468553936935565</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.9671125975473801</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9431654676258993</v>
+        <v>0.9602044541803578</v>
       </c>
       <c r="G8" t="n">
-        <v>0.971830985915493</v>
+        <v>0.9747961452928094</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9572836801752465</v>
+        <v>0.9674452823248115</v>
       </c>
       <c r="I8" t="n">
-        <v>57.56788086891174</v>
+        <v>41.96751761436462</v>
       </c>
     </row>
     <row r="9">
@@ -683,28 +671,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.09607746068182031</v>
+        <v>0.07860993961028666</v>
       </c>
       <c r="C9" t="n">
         <v>0.0009879583809693736</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08983477648105141</v>
+        <v>0.08600454236044598</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9682274247491639</v>
+        <v>0.9665551839464883</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9698772777984381</v>
+        <v>0.9765329295987888</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9666419570051891</v>
+        <v>0.9562638991845812</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9682569147948765</v>
+        <v>0.9662921348314607</v>
       </c>
       <c r="I9" t="n">
-        <v>58.19933247566223</v>
+        <v>41.99972701072693</v>
       </c>
     </row>
     <row r="10">
@@ -712,28 +700,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.08153630713281812</v>
+        <v>0.06024836001479735</v>
       </c>
       <c r="C10" t="n">
         <v>0.0009842915805643154</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09562709602973694</v>
+        <v>0.08223139981810863</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9645113340765514</v>
+        <v>0.967670011148272</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9576487769258853</v>
+        <v>0.9805788271134805</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9722016308376575</v>
+        <v>0.9544106745737584</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9648703329041751</v>
+        <v>0.9673178061607813</v>
       </c>
       <c r="I10" t="n">
-        <v>58.23950123786926</v>
+        <v>42.12685799598694</v>
       </c>
     </row>
     <row r="11">
@@ -741,28 +729,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.07193040213980788</v>
+        <v>0.04878720311722324</v>
       </c>
       <c r="C11" t="n">
         <v>0.0009801468428384714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.09398235142308138</v>
+        <v>0.08834586443569643</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9643255295429208</v>
+        <v>0.9671125975473801</v>
       </c>
       <c r="F11" t="n">
-        <v>0.976425855513308</v>
+        <v>0.959533357637623</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9518161601186064</v>
+        <v>0.9755374351371386</v>
       </c>
       <c r="H11" t="n">
-        <v>0.963963963963964</v>
+        <v>0.9674692152177908</v>
       </c>
       <c r="I11" t="n">
-        <v>57.69978213310242</v>
+        <v>42.1274745464325</v>
       </c>
     </row>
     <row r="12">
@@ -770,28 +758,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0777846432846582</v>
+        <v>0.05395238078147433</v>
       </c>
       <c r="C12" t="n">
         <v>0.0009755282581475767</v>
       </c>
       <c r="D12" t="n">
-        <v>0.07602150640319537</v>
+        <v>0.119932429695546</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9721293199554069</v>
+        <v>0.9643255295429208</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9729027468448403</v>
+        <v>0.9793420045906657</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9714603409933283</v>
+        <v>0.9488510007412898</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9721810089020771</v>
+        <v>0.963855421686747</v>
       </c>
       <c r="I12" t="n">
-        <v>57.31345915794373</v>
+        <v>42.09525060653687</v>
       </c>
     </row>
     <row r="13">
@@ -799,28 +787,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.05982968003529208</v>
+        <v>0.05102219623713311</v>
       </c>
       <c r="C13" t="n">
         <v>0.0009704403844771127</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07096768112318623</v>
+        <v>0.03966545803178262</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9739873652917131</v>
+        <v>0.9842066146413972</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9691856199559794</v>
+        <v>0.9815702174714338</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9792438843587843</v>
+        <v>0.9870274277242401</v>
       </c>
       <c r="H13" t="n">
-        <v>0.974188790560472</v>
+        <v>0.9842912585474034</v>
       </c>
       <c r="I13" t="n">
-        <v>57.36174488067627</v>
+        <v>42.1019115447998</v>
       </c>
     </row>
     <row r="14">
@@ -828,28 +816,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0925142996247206</v>
+        <v>0.03785293676164696</v>
       </c>
       <c r="C14" t="n">
         <v>0.0009648882429441257</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0713222080086683</v>
+        <v>0.04693633049847724</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9764028242289112</v>
+        <v>0.9816053511705686</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9791278419679463</v>
+        <v>0.9898228420655861</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9736842105263158</v>
+        <v>0.9733135656041513</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9763984389518677</v>
+        <v>0.9814987852737806</v>
       </c>
       <c r="I14" t="n">
-        <v>57.40774321556091</v>
+        <v>42.24591684341431</v>
       </c>
     </row>
     <row r="15">
@@ -857,28 +845,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.06657687002425546</v>
+        <v>0.03148233132104059</v>
       </c>
       <c r="C15" t="n">
         <v>0.0009588773128419905</v>
       </c>
       <c r="D15" t="n">
-        <v>0.06501142385266942</v>
+        <v>0.04882782760397228</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9752879970271274</v>
+        <v>0.9830917874396136</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9709878810135879</v>
+        <v>0.981529368304396</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9799851742031134</v>
+        <v>0.9848035581912528</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9754657812211769</v>
+        <v>0.983163737280296</v>
       </c>
       <c r="I15" t="n">
-        <v>56.91695022583008</v>
+        <v>42.20737862586975</v>
       </c>
     </row>
     <row r="16">
@@ -886,28 +874,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.04409820880759217</v>
+        <v>0.0299485850070581</v>
       </c>
       <c r="C16" t="n">
         <v>0.0009524135262330098</v>
       </c>
       <c r="D16" t="n">
-        <v>0.09624473661867648</v>
+        <v>0.05096445293566997</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9652545522110739</v>
+        <v>0.9817911557041992</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9860627177700348</v>
+        <v>0.973415877640204</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9440326167531505</v>
+        <v>0.9907338769458859</v>
       </c>
       <c r="H16" t="n">
-        <v>0.964590039765196</v>
+        <v>0.9819985304922851</v>
       </c>
       <c r="I16" t="n">
-        <v>57.19852757453918</v>
+        <v>42.22123837471008</v>
       </c>
     </row>
     <row r="17">
@@ -915,28 +903,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.04021747095902509</v>
+        <v>0.02900416727515455</v>
       </c>
       <c r="C17" t="n">
         <v>0.0009455032620941839</v>
       </c>
       <c r="D17" t="n">
-        <v>0.065050248306702</v>
+        <v>0.0547099258979633</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9780750650315868</v>
+        <v>0.9821627647714605</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9690909090909091</v>
+        <v>0.9811390532544378</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9877687175685693</v>
+        <v>0.9833209785025945</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9783406754772394</v>
+        <v>0.9822288041466124</v>
       </c>
       <c r="I17" t="n">
-        <v>56.90705132484436</v>
+        <v>42.14786434173584</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +932,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.03680263245979049</v>
+        <v>0.03077004264681572</v>
       </c>
       <c r="C18" t="n">
         <v>0.0009381533400219318</v>
       </c>
       <c r="D18" t="n">
-        <v>0.054796467547597</v>
+        <v>0.047786596922766</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9806763285024155</v>
+        <v>0.9847640282422891</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9901738473167044</v>
+        <v>0.9819454679439941</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9710896960711638</v>
+        <v>0.9877687175685693</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9805389221556886</v>
+        <v>0.9848484848484849</v>
       </c>
       <c r="I18" t="n">
-        <v>56.89948415756226</v>
+        <v>42.1971697807312</v>
       </c>
     </row>
     <row r="19">
@@ -973,28 +961,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0384828590942418</v>
+        <v>0.02683988414216089</v>
       </c>
       <c r="C19" t="n">
         <v>0.0009303710135019719</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06310064199562432</v>
+        <v>0.03310793641398072</v>
       </c>
       <c r="E19" t="n">
-        <v>0.978446674098848</v>
+        <v>0.9890375325157934</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9701383831026948</v>
+        <v>0.9921671018276762</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9873980726464048</v>
+        <v>0.9859154929577465</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9786921381337252</v>
+        <v>0.9890314184792712</v>
       </c>
       <c r="I19" t="n">
-        <v>57.72803020477295</v>
+        <v>42.21122717857361</v>
       </c>
     </row>
     <row r="20">
@@ -1002,28 +990,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.03449934953668004</v>
+        <v>0.02451893205412262</v>
       </c>
       <c r="C20" t="n">
         <v>0.0009221639627510076</v>
       </c>
       <c r="D20" t="n">
-        <v>0.06004121789216896</v>
+        <v>0.028934609733762</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9780750650315868</v>
+        <v>0.9890375325157934</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9817027632561613</v>
+        <v>0.9856459330143541</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9744255003706449</v>
+        <v>0.9925871015567087</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9780505952380952</v>
+        <v>0.9891043397968605</v>
       </c>
       <c r="I20" t="n">
-        <v>56.68240070343018</v>
+        <v>42.25726437568665</v>
       </c>
     </row>
     <row r="21">
@@ -1031,28 +1019,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.032237355429981</v>
+        <v>0.02118756841812657</v>
       </c>
       <c r="C21" t="n">
         <v>0.000913540287137281</v>
       </c>
       <c r="D21" t="n">
-        <v>0.05046699118157078</v>
+        <v>0.05103980807312654</v>
       </c>
       <c r="E21" t="n">
-        <v>0.981419546636938</v>
+        <v>0.9825343738387217</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9814677538917717</v>
+        <v>0.9700361010830325</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9814677538917717</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9814677538917717</v>
+        <v>0.9828090709583028</v>
       </c>
       <c r="I21" t="n">
-        <v>56.79534721374512</v>
+        <v>42.140700340271</v>
       </c>
     </row>
     <row r="22">
@@ -1060,28 +1048,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.02555134575616812</v>
+        <v>0.02147500257730054</v>
       </c>
       <c r="C22" t="n">
         <v>0.0009045084971874739</v>
       </c>
       <c r="D22" t="n">
-        <v>0.04473031582376236</v>
+        <v>0.0314243040908646</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9855072463768116</v>
+        <v>0.9890375325157934</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9902694610778443</v>
+        <v>0.9845758354755784</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9807264640474426</v>
+        <v>0.9936990363232023</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9854748603351955</v>
+        <v>0.9891163991883416</v>
       </c>
       <c r="I22" t="n">
-        <v>56.62403750419617</v>
+        <v>42.35974550247192</v>
       </c>
     </row>
     <row r="23">
@@ -1089,28 +1077,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.02829775390502624</v>
+        <v>0.01883163891506652</v>
       </c>
       <c r="C23" t="n">
         <v>0.0008950775061878453</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03455718226139103</v>
+        <v>0.03702437720838769</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9873652917131178</v>
+        <v>0.9871794871794872</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9863165680473372</v>
+        <v>0.9799196787148594</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9885100074128984</v>
+        <v>0.9948109710896961</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9874120696038504</v>
+        <v>0.9873091778554349</v>
       </c>
       <c r="I23" t="n">
-        <v>56.56816124916077</v>
+        <v>42.18388414382935</v>
       </c>
     </row>
     <row r="24">
@@ -1118,28 +1106,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.02654931630675365</v>
+        <v>0.01983870070967966</v>
       </c>
       <c r="C24" t="n">
         <v>0.0008852566213878948</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04492635999636769</v>
+        <v>0.02278811282526449</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9838350055741361</v>
+        <v>0.9918246005202527</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9906050357008643</v>
+        <v>0.9922106824925816</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9770200148257969</v>
+        <v>0.991475166790215</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9837656279156559</v>
+        <v>0.9918427882832778</v>
       </c>
       <c r="I24" t="n">
-        <v>56.60618042945862</v>
+        <v>42.13731145858765</v>
       </c>
     </row>
     <row r="25">
@@ -1147,28 +1135,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.02454154691354686</v>
+        <v>0.01524940144951463</v>
       </c>
       <c r="C25" t="n">
         <v>0.0008750555348152299</v>
       </c>
       <c r="D25" t="n">
-        <v>0.04787763265859109</v>
+        <v>0.0481172410418905</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9858788554440728</v>
+        <v>0.9838350055741361</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9888143176733781</v>
+        <v>0.9738656987295826</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9829503335804299</v>
+        <v>0.9944403261675315</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9858736059479554</v>
+        <v>0.9840454795525398</v>
       </c>
       <c r="I25" t="n">
-        <v>56.44465780258179</v>
+        <v>42.15412282943726</v>
       </c>
     </row>
     <row r="26">
@@ -1176,28 +1164,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.02557472076768863</v>
+        <v>0.01683188815809681</v>
       </c>
       <c r="C26" t="n">
         <v>0.0008644843137107058</v>
       </c>
       <c r="D26" t="n">
-        <v>0.04873809545153143</v>
+        <v>0.05167891972685527</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9866220735785953</v>
+        <v>0.9808621330360461</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9939804364183596</v>
+        <v>0.9916635089048882</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9792438843587843</v>
+        <v>0.9699777613046702</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9865571321882002</v>
+        <v>0.9807007682218475</v>
       </c>
       <c r="I26" t="n">
-        <v>56.46183466911316</v>
+        <v>42.24277544021606</v>
       </c>
     </row>
     <row r="27">
@@ -1205,28 +1193,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.02441946140353905</v>
+        <v>0.01776743915154854</v>
       </c>
       <c r="C27" t="n">
         <v>0.0008535533905932738</v>
       </c>
       <c r="D27" t="n">
-        <v>0.05452531661530723</v>
+        <v>0.0318979773036135</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9821627647714605</v>
+        <v>0.9910813823857302</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9879969992498124</v>
+        <v>0.9882092851879145</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9762787249814677</v>
+        <v>0.994069681245367</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9821029082774049</v>
+        <v>0.991130820399113</v>
       </c>
       <c r="I27" t="n">
-        <v>56.50344300270081</v>
+        <v>42.02890157699585</v>
       </c>
     </row>
     <row r="28">
@@ -1234,28 +1222,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.01877051440953672</v>
+        <v>0.01436415554992203</v>
       </c>
       <c r="C28" t="n">
         <v>0.0008422735529643445</v>
       </c>
       <c r="D28" t="n">
-        <v>0.04677215450606154</v>
+        <v>0.02571404745746142</v>
       </c>
       <c r="E28" t="n">
-        <v>0.987736900780379</v>
+        <v>0.9899665551839465</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9899478778853313</v>
+        <v>0.9899925871015567</v>
       </c>
       <c r="G28" t="n">
-        <v>0.985544848035582</v>
+        <v>0.9899925871015567</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9877414561664191</v>
+        <v>0.9899925871015567</v>
       </c>
       <c r="I28" t="n">
-        <v>56.36156272888184</v>
+        <v>42.23304414749146</v>
       </c>
     </row>
     <row r="29">
@@ -1263,28 +1251,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.01734704390196688</v>
+        <v>0.01212860781639827</v>
       </c>
       <c r="C29" t="n">
         <v>0.000830655932661826</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1100134319965397</v>
+        <v>0.02390168406638095</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9697138610182089</v>
+        <v>0.9923820141211446</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9703153988868275</v>
+        <v>0.9911275415896488</v>
       </c>
       <c r="G29" t="n">
-        <v>0.969236471460341</v>
+        <v>0.9936990363232023</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9697756350825144</v>
+        <v>0.9924116231723117</v>
       </c>
       <c r="I29" t="n">
-        <v>56.62909054756165</v>
+        <v>40.02386593818665</v>
       </c>
     </row>
     <row r="30">
@@ -1292,28 +1280,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01817366908691478</v>
+        <v>0.01043183780471563</v>
       </c>
       <c r="C30" t="n">
         <v>0.000818711994874345</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03990318379962483</v>
+        <v>0.02796218023136592</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9875510962467484</v>
+        <v>0.9912671869193609</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9899441340782122</v>
+        <v>0.9970003749531309</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9851742031134173</v>
+        <v>0.985544848035582</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9875534088798068</v>
+        <v>0.9912395153774464</v>
       </c>
       <c r="I30" t="n">
-        <v>56.55908417701721</v>
+        <v>38.89034008979797</v>
       </c>
     </row>
     <row r="31">
@@ -1321,28 +1309,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.01750512867124632</v>
+        <v>0.0140718445527387</v>
       </c>
       <c r="C31" t="n">
         <v>0.0008064535268264884</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0541609216561698</v>
+        <v>0.02438395097807624</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9838350055741361</v>
+        <v>0.9916387959866221</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9891345073061072</v>
+        <v>0.9907510173880874</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9785025945144552</v>
+        <v>0.9925871015567087</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9837898267188373</v>
+        <v>0.9916682095908165</v>
       </c>
       <c r="I31" t="n">
-        <v>56.47380495071411</v>
+        <v>38.62277817726135</v>
       </c>
     </row>
     <row r="32">
@@ -1350,28 +1338,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.01341858971866688</v>
+        <v>0.009611376848968043</v>
       </c>
       <c r="C32" t="n">
         <v>0.0007938926261462368</v>
       </c>
       <c r="D32" t="n">
-        <v>0.04776027434107798</v>
+        <v>0.04077567086607933</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9842066146413972</v>
+        <v>0.9886659234485321</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9840681733975547</v>
+        <v>0.9792802617230099</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9844329132690882</v>
+        <v>0.9985174203113417</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9842505095423383</v>
+        <v>0.988805285373463</v>
       </c>
       <c r="I32" t="n">
-        <v>56.34465980529785</v>
+        <v>38.80953669548035</v>
       </c>
     </row>
     <row r="33">
@@ -1379,28 +1367,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.01484235871435023</v>
+        <v>0.009834232833167264</v>
       </c>
       <c r="C33" t="n">
         <v>0.0007810416889260655</v>
       </c>
       <c r="D33" t="n">
-        <v>0.03604023733678117</v>
+        <v>0.01580016180283974</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9901523597175771</v>
+        <v>0.9944258639910813</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9914529914529915</v>
+        <v>0.9911634756995582</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9888806523350631</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9901651512339952</v>
+        <v>0.9944588104913188</v>
       </c>
       <c r="I33" t="n">
-        <v>56.32007265090942</v>
+        <v>38.77276110649109</v>
       </c>
     </row>
     <row r="34">
@@ -1408,28 +1396,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.01807017826405763</v>
+        <v>0.0095417940799578</v>
       </c>
       <c r="C34" t="n">
         <v>0.0007679133974894984</v>
       </c>
       <c r="D34" t="n">
-        <v>0.04382461611501468</v>
+        <v>0.03118999320183197</v>
       </c>
       <c r="E34" t="n">
-        <v>0.987736900780379</v>
+        <v>0.9895949461166852</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9831130690161527</v>
+        <v>0.9856617647058824</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9925871015567087</v>
+        <v>0.9936990363232023</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9878273699741793</v>
+        <v>0.9896640826873385</v>
       </c>
       <c r="I34" t="n">
-        <v>56.83648061752319</v>
+        <v>38.76857686042786</v>
       </c>
     </row>
     <row r="35">
@@ -1437,28 +1425,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.01048891368831943</v>
+        <v>0.009999452327233477</v>
       </c>
       <c r="C35" t="n">
         <v>0.0007545207078751858</v>
       </c>
       <c r="D35" t="n">
-        <v>0.02624776094215326</v>
+        <v>0.08965112398359264</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9912671869193609</v>
+        <v>0.9791898922333705</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9922020051986632</v>
+        <v>0.9927591463414634</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9903632320237212</v>
+        <v>0.9655300222386953</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9912817659061398</v>
+        <v>0.9789552799699361</v>
       </c>
       <c r="I35" t="n">
-        <v>57.21406698226929</v>
+        <v>38.84347701072693</v>
       </c>
     </row>
     <row r="36">
@@ -1466,28 +1454,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.01441022704818215</v>
+        <v>0.009846166700877764</v>
       </c>
       <c r="C36" t="n">
         <v>0.0007408768370508578</v>
       </c>
       <c r="D36" t="n">
-        <v>0.03662125234645908</v>
+        <v>0.02046623488827181</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9894091415830546</v>
+        <v>0.9934968413229283</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9867305565794323</v>
+        <v>0.9886238532110092</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9922164566345441</v>
+        <v>0.9985174203113417</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9894659027906118</v>
+        <v>0.9935460077447907</v>
       </c>
       <c r="I36" t="n">
-        <v>56.17349243164062</v>
+        <v>38.78760576248169</v>
       </c>
     </row>
     <row r="37">
@@ -1495,28 +1483,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.01163417196915227</v>
+        <v>0.007880744708142358</v>
       </c>
       <c r="C37" t="n">
         <v>0.0007269952498697736</v>
       </c>
       <c r="D37" t="n">
-        <v>0.033862248978136</v>
+        <v>0.03406761239625532</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9910813823857302</v>
+        <v>0.990709773318469</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9885693215339233</v>
+        <v>0.9925595238095238</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9936990363232023</v>
+        <v>0.9888806523350631</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9911275415896488</v>
+        <v>0.9907166728555514</v>
       </c>
       <c r="I37" t="n">
-        <v>56.35261607170105</v>
+        <v>38.93117380142212</v>
       </c>
     </row>
     <row r="38">
@@ -1524,28 +1512,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.0109403383850985</v>
+        <v>0.009158662447258355</v>
       </c>
       <c r="C38" t="n">
         <v>0.0007128896457825365</v>
       </c>
       <c r="D38" t="n">
-        <v>0.03570431047448986</v>
+        <v>0.02571047282942706</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9903381642512077</v>
+        <v>0.9901523597175771</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9878318584070797</v>
+        <v>0.9907235621521335</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9929577464788732</v>
+        <v>0.9896219421793921</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9903881700554529</v>
+        <v>0.9901724457630261</v>
       </c>
       <c r="I38" t="n">
-        <v>56.26181578636169</v>
+        <v>38.60432171821594</v>
       </c>
     </row>
     <row r="39">
@@ -1553,28 +1541,28 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.01028894460351555</v>
+        <v>0.006815528149167476</v>
       </c>
       <c r="C39" t="n">
         <v>0.0006985739453173904</v>
       </c>
       <c r="D39" t="n">
-        <v>0.02900949164084727</v>
+        <v>0.01959616335486623</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9914529914529915</v>
+        <v>0.9933110367892977</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9896602658788775</v>
+        <v>0.9922337278106509</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.9944403261675315</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9914909359970403</v>
+        <v>0.9933358015549797</v>
       </c>
       <c r="I39" t="n">
-        <v>56.27567934989929</v>
+        <v>38.80601191520691</v>
       </c>
     </row>
     <row r="40">
@@ -1582,28 +1570,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.01132334678720477</v>
+        <v>0.007423808690805987</v>
       </c>
       <c r="C40" t="n">
         <v>0.0006840622763423392</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0367460837213153</v>
+        <v>0.0193716680037276</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9869936826458565</v>
+        <v>0.9944258639910813</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9910313901345291</v>
+        <v>0.9940740740740741</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9829503335804299</v>
+        <v>0.9948109710896961</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9869743208038705</v>
+        <v>0.9944423860689144</v>
       </c>
       <c r="I40" t="n">
-        <v>56.59071469306946</v>
+        <v>38.58547520637512</v>
       </c>
     </row>
     <row r="41">
@@ -1611,28 +1599,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>0.01129587067703243</v>
+        <v>0.009126694145712709</v>
       </c>
       <c r="C41" t="n">
         <v>0.0006693689601226459</v>
       </c>
       <c r="D41" t="n">
-        <v>0.04214596286841073</v>
+        <v>0.02021331481327139</v>
       </c>
       <c r="E41" t="n">
-        <v>0.986250464511334</v>
+        <v>0.9929394277220365</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9899178491411501</v>
+        <v>0.9929577464788732</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9825796886582654</v>
+        <v>0.9929577464788732</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9862351190476191</v>
+        <v>0.9929577464788732</v>
       </c>
       <c r="I41" t="n">
-        <v>56.63305950164795</v>
+        <v>38.58873534202576</v>
       </c>
     </row>
     <row r="42">
@@ -1640,28 +1628,28 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.009658126655171517</v>
+        <v>0.006314253321592573</v>
       </c>
       <c r="C42" t="n">
         <v>0.0006545084971874739</v>
       </c>
       <c r="D42" t="n">
-        <v>0.03994379557187765</v>
+        <v>0.0189687171784375</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9894091415830546</v>
+        <v>0.9947974730583427</v>
       </c>
       <c r="F42" t="n">
-        <v>0.990709773318469</v>
+        <v>0.9970215934475056</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9881393624907339</v>
+        <v>0.9925871015567087</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9894228984969382</v>
+        <v>0.9947994056463596</v>
       </c>
       <c r="I42" t="n">
-        <v>56.2373218536377</v>
+        <v>38.70598697662354</v>
       </c>
     </row>
     <row r="43">
@@ -1669,28 +1657,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.007396745248780512</v>
+        <v>0.003466155077833017</v>
       </c>
       <c r="C43" t="n">
         <v>0.0006394955530196148</v>
       </c>
       <c r="D43" t="n">
-        <v>0.04018038970751354</v>
+        <v>0.01420729720141971</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9888517279821628</v>
+        <v>0.9959123002601263</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9940074906367041</v>
+        <v>0.9988814317673378</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9836916234247591</v>
+        <v>0.9929577464788732</v>
       </c>
       <c r="H43" t="n">
-        <v>0.988822652757079</v>
+        <v>0.995910780669145</v>
       </c>
       <c r="I43" t="n">
-        <v>56.2947952747345</v>
+        <v>38.62316155433655</v>
       </c>
     </row>
     <row r="44">
@@ -1698,28 +1686,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.007498881922073388</v>
+        <v>0.005466206949496393</v>
       </c>
       <c r="C44" t="n">
         <v>0.0006243449435824275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.03642087601444349</v>
+        <v>0.02727762450402321</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9895949461166852</v>
+        <v>0.9927536231884058</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9903489235337788</v>
+        <v>0.9966380276428838</v>
       </c>
       <c r="G44" t="n">
         <v>0.9888806523350631</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9896142433234422</v>
+        <v>0.9927441860465116</v>
       </c>
       <c r="I44" t="n">
-        <v>56.30850458145142</v>
+        <v>38.84274220466614</v>
       </c>
     </row>
     <row r="45">
@@ -1727,28 +1715,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.005460563013792242</v>
+        <v>0.007074329023059916</v>
       </c>
       <c r="C45" t="n">
         <v>0.0006090716206982715</v>
       </c>
       <c r="D45" t="n">
-        <v>0.03654189027812802</v>
+        <v>0.02188420031304234</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9934968413229283</v>
+        <v>0.9931252322556671</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9936967000370782</v>
+        <v>0.9947936035701004</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.991475166790215</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9935125115848007</v>
+        <v>0.9931316131427511</v>
       </c>
       <c r="I45" t="n">
-        <v>56.7107310295105</v>
+        <v>38.67405271530151</v>
       </c>
     </row>
     <row r="46">
@@ -1756,28 +1744,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>0.0086846796100165</v>
+        <v>0.005007074553725133</v>
       </c>
       <c r="C46" t="n">
         <v>0.0005936906572928626</v>
       </c>
       <c r="D46" t="n">
-        <v>0.05417142201035885</v>
+        <v>0.02107261620054735</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9842066146413972</v>
+        <v>0.9946116685247121</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9913501316284318</v>
+        <v>0.9944423860689144</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9770200148257969</v>
+        <v>0.9948109710896961</v>
       </c>
       <c r="H46" t="n">
-        <v>0.984132910210939</v>
+        <v>0.9946266444320919</v>
       </c>
       <c r="I46" t="n">
-        <v>56.43192219734192</v>
+        <v>38.65310215950012</v>
       </c>
     </row>
     <row r="47">
@@ -1785,28 +1773,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.00690870995523312</v>
+        <v>0.004349934701766861</v>
       </c>
       <c r="C47" t="n">
         <v>0.0005782172325201157</v>
       </c>
       <c r="D47" t="n">
-        <v>0.04608345356422508</v>
+        <v>0.01723806033940225</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9882943143812709</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9917879805897724</v>
+        <v>0.9937176644493718</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9848035581912528</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9882834294216105</v>
+        <v>0.9951887490747594</v>
       </c>
       <c r="I47" t="n">
-        <v>56.12800788879395</v>
+        <v>38.60030150413513</v>
       </c>
     </row>
     <row r="48">
@@ -1814,28 +1802,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.006438551228119985</v>
+        <v>0.004996662863853753</v>
       </c>
       <c r="C48" t="n">
         <v>0.0005626666167821524</v>
       </c>
       <c r="D48" t="n">
-        <v>0.02977467549777354</v>
+        <v>0.02269347437746794</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9931252322556671</v>
+        <v>0.9929394277220365</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9929603556872916</v>
+        <v>0.9958985831469053</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.9899925871015567</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9931443394478414</v>
+        <v>0.9929368029739777</v>
       </c>
       <c r="I48" t="n">
-        <v>56.32784628868103</v>
+        <v>38.71304202079773</v>
       </c>
     </row>
     <row r="49">
@@ -1843,28 +1831,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.005694671136230966</v>
+        <v>0.002997512387901799</v>
       </c>
       <c r="C49" t="n">
         <v>0.0005470541566592573</v>
       </c>
       <c r="D49" t="n">
-        <v>0.03442680129565821</v>
+        <v>0.02530514939451694</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9918246005202527</v>
+        <v>0.9927536231884058</v>
       </c>
       <c r="F49" t="n">
-        <v>0.987151248164464</v>
+        <v>0.9947897283215482</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9907338769458859</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9918849133161195</v>
+        <v>0.992757660167131</v>
       </c>
       <c r="I49" t="n">
-        <v>56.35917401313782</v>
+        <v>38.62094521522522</v>
       </c>
     </row>
     <row r="50">
@@ -1872,28 +1860,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.007816365695979122</v>
+        <v>0.005734068475998623</v>
       </c>
       <c r="C50" t="n">
         <v>0.000531395259764657</v>
       </c>
       <c r="D50" t="n">
-        <v>0.02865481009603872</v>
+        <v>0.01433230929558854</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9908955778520996</v>
+        <v>0.9955406911928651</v>
       </c>
       <c r="F50" t="n">
-        <v>0.992196209587514</v>
+        <v>0.9940872135994088</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9896219421793921</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9909074039710521</v>
+        <v>0.9955588452997779</v>
       </c>
       <c r="I50" t="n">
-        <v>56.39493560791016</v>
+        <v>38.65184736251831</v>
       </c>
     </row>
     <row r="51">
@@ -1901,28 +1889,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.005384539628358266</v>
+        <v>0.002037930873724965</v>
       </c>
       <c r="C51" t="n">
         <v>0.0005157053795390644</v>
       </c>
       <c r="D51" t="n">
-        <v>0.03828306741584209</v>
+        <v>0.03683017536747237</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9890375325157934</v>
+        <v>0.9905239687848384</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9896103896103896</v>
+        <v>0.9853318665199853</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9885100074128984</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H51" t="n">
-        <v>0.98905989245318</v>
+        <v>0.9905990783410138</v>
       </c>
       <c r="I51" t="n">
-        <v>57.16832137107849</v>
+        <v>38.53095483779907</v>
       </c>
     </row>
   </sheetData>
